--- a/rules/CORE-000709/negative/01/data/unit-test-coreid-FB0607-negative.xlsx
+++ b/rules/CORE-000709/negative/01/data/unit-test-coreid-FB0607-negative.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulieChason\GitHub\core-contributor\rules\CORE-000709\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7FBB11-F341-452D-8889-69D6ED4F6860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BB127B-FC59-41DE-9771-7E7493BC1389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="105">
   <si>
     <t>Product</t>
   </si>
@@ -391,7 +391,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,12 +402,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -468,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -500,25 +494,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -908,118 +889,112 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A2" s="15">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="13">
         <v>5</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="15"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A3" s="15">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="13">
         <v>5</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>102</v>
-      </c>
+      <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="15">
+      <c r="A4" s="13">
         <v>1</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="13">
         <v>5</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="15"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A5" s="15">
+      <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="13">
         <v>6</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="15"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A6" s="15">
+      <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="13">
         <v>6</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="15" t="s">
-        <v>103</v>
-      </c>
+      <c r="F6" s="13"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="15">
+      <c r="A7" s="13">
         <v>2</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="B7" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <v>6</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>102</v>
-      </c>
+      <c r="F7" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1425,77 +1400,77 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="19" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:26" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="7">
         <v>1211</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="17">
+      <c r="L6" s="6"/>
+      <c r="M6" s="7">
         <v>701</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="7">
         <v>1955</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="O6" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="P6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="Q6" s="16" t="s">
+      <c r="Q6" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="R6" s="16" t="s">
+      <c r="R6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S6" s="16" t="s">
+      <c r="S6" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="T6" s="16" t="s">
+      <c r="T6" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="U6" s="16" t="s">
+      <c r="U6" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="V6" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="W6" s="16" t="s">
+      <c r="W6" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16" t="s">
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1602,7 +1577,7 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>102</v>
       </c>
       <c r="F5" s="14"/>
@@ -1620,10 +1595,10 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>102</v>
       </c>
     </row>
